--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440335</v>
+        <v>113440333</v>
       </c>
       <c r="B2" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772748</v>
+        <v>772804</v>
       </c>
       <c r="R2" t="n">
-        <v>7203574</v>
+        <v>7203582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440333</v>
+        <v>113440334</v>
       </c>
       <c r="B3" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772804</v>
+        <v>772789</v>
       </c>
       <c r="R3" t="n">
-        <v>7203582</v>
+        <v>7203583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440336</v>
+        <v>113440335</v>
       </c>
       <c r="B4" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772757</v>
+        <v>772748</v>
       </c>
       <c r="R4" t="n">
-        <v>7203587</v>
+        <v>7203574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440334</v>
+        <v>113440336</v>
       </c>
       <c r="B5" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772789</v>
+        <v>772757</v>
       </c>
       <c r="R5" t="n">
-        <v>7203583</v>
+        <v>7203587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440333</v>
+        <v>113440334</v>
       </c>
       <c r="B2" t="n">
         <v>90045</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772804</v>
+        <v>772789</v>
       </c>
       <c r="R2" t="n">
-        <v>7203582</v>
+        <v>7203583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440334</v>
+        <v>113440333</v>
       </c>
       <c r="B3" t="n">
         <v>90045</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772789</v>
+        <v>772804</v>
       </c>
       <c r="R3" t="n">
-        <v>7203583</v>
+        <v>7203582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440334</v>
+        <v>113440333</v>
       </c>
       <c r="B2" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772789</v>
+        <v>772804</v>
       </c>
       <c r="R2" t="n">
-        <v>7203583</v>
+        <v>7203582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440333</v>
+        <v>113440334</v>
       </c>
       <c r="B3" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772804</v>
+        <v>772789</v>
       </c>
       <c r="R3" t="n">
-        <v>7203582</v>
+        <v>7203583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>113440335</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>113440336</v>
       </c>
       <c r="B5" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440333</v>
+        <v>113440334</v>
       </c>
       <c r="B2" t="n">
         <v>90057</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772804</v>
+        <v>772789</v>
       </c>
       <c r="R2" t="n">
-        <v>7203582</v>
+        <v>7203583</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440334</v>
+        <v>113440336</v>
       </c>
       <c r="B3" t="n">
         <v>90057</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772789</v>
+        <v>772757</v>
       </c>
       <c r="R3" t="n">
-        <v>7203583</v>
+        <v>7203587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440335</v>
+        <v>113440333</v>
       </c>
       <c r="B4" t="n">
         <v>90057</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772748</v>
+        <v>772804</v>
       </c>
       <c r="R4" t="n">
-        <v>7203574</v>
+        <v>7203582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440336</v>
+        <v>113440335</v>
       </c>
       <c r="B5" t="n">
         <v>90057</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772757</v>
+        <v>772748</v>
       </c>
       <c r="R5" t="n">
-        <v>7203587</v>
+        <v>7203574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440334</v>
+        <v>113440336</v>
       </c>
       <c r="B2" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772789</v>
+        <v>772757</v>
       </c>
       <c r="R2" t="n">
-        <v>7203583</v>
+        <v>7203587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440336</v>
+        <v>113440335</v>
       </c>
       <c r="B3" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772757</v>
+        <v>772748</v>
       </c>
       <c r="R3" t="n">
-        <v>7203587</v>
+        <v>7203574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>113440333</v>
       </c>
       <c r="B4" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440335</v>
+        <v>113440334</v>
       </c>
       <c r="B5" t="n">
-        <v>90057</v>
+        <v>90079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772748</v>
+        <v>772789</v>
       </c>
       <c r="R5" t="n">
-        <v>7203574</v>
+        <v>7203583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440336</v>
+        <v>113440335</v>
       </c>
       <c r="B2" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772757</v>
+        <v>772748</v>
       </c>
       <c r="R2" t="n">
-        <v>7203587</v>
+        <v>7203574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440335</v>
+        <v>113440334</v>
       </c>
       <c r="B3" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772748</v>
+        <v>772789</v>
       </c>
       <c r="R3" t="n">
-        <v>7203574</v>
+        <v>7203583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>113440333</v>
       </c>
       <c r="B4" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440334</v>
+        <v>113440336</v>
       </c>
       <c r="B5" t="n">
-        <v>90079</v>
+        <v>90083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772789</v>
+        <v>772757</v>
       </c>
       <c r="R5" t="n">
-        <v>7203583</v>
+        <v>7203587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113440335</v>
       </c>
       <c r="B2" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440334</v>
+        <v>113440333</v>
       </c>
       <c r="B3" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772789</v>
+        <v>772804</v>
       </c>
       <c r="R3" t="n">
-        <v>7203583</v>
+        <v>7203582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440333</v>
+        <v>113440334</v>
       </c>
       <c r="B4" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772804</v>
+        <v>772789</v>
       </c>
       <c r="R4" t="n">
-        <v>7203582</v>
+        <v>7203583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>113440336</v>
       </c>
       <c r="B5" t="n">
-        <v>90083</v>
+        <v>90089</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440335</v>
+        <v>113440336</v>
       </c>
       <c r="B2" t="n">
         <v>90089</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772748</v>
+        <v>772757</v>
       </c>
       <c r="R2" t="n">
-        <v>7203574</v>
+        <v>7203587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440334</v>
+        <v>113440335</v>
       </c>
       <c r="B4" t="n">
         <v>90089</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772789</v>
+        <v>772748</v>
       </c>
       <c r="R4" t="n">
-        <v>7203583</v>
+        <v>7203574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440336</v>
+        <v>113440334</v>
       </c>
       <c r="B5" t="n">
         <v>90089</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772757</v>
+        <v>772789</v>
       </c>
       <c r="R5" t="n">
-        <v>7203587</v>
+        <v>7203583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440336</v>
+        <v>113440335</v>
       </c>
       <c r="B2" t="n">
-        <v>90089</v>
+        <v>90096</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772757</v>
+        <v>772748</v>
       </c>
       <c r="R2" t="n">
-        <v>7203587</v>
+        <v>7203574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440333</v>
+        <v>113440334</v>
       </c>
       <c r="B3" t="n">
-        <v>90089</v>
+        <v>90096</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772804</v>
+        <v>772789</v>
       </c>
       <c r="R3" t="n">
-        <v>7203582</v>
+        <v>7203583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440335</v>
+        <v>113440333</v>
       </c>
       <c r="B4" t="n">
-        <v>90089</v>
+        <v>90096</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772748</v>
+        <v>772804</v>
       </c>
       <c r="R4" t="n">
-        <v>7203574</v>
+        <v>7203582</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440334</v>
+        <v>113440336</v>
       </c>
       <c r="B5" t="n">
-        <v>90089</v>
+        <v>90096</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772789</v>
+        <v>772757</v>
       </c>
       <c r="R5" t="n">
-        <v>7203583</v>
+        <v>7203587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440335</v>
+        <v>113440336</v>
       </c>
       <c r="B2" t="n">
-        <v>90096</v>
+        <v>90099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772748</v>
+        <v>772757</v>
       </c>
       <c r="R2" t="n">
-        <v>7203574</v>
+        <v>7203587</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440334</v>
+        <v>113440333</v>
       </c>
       <c r="B3" t="n">
-        <v>90096</v>
+        <v>90099</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772789</v>
+        <v>772804</v>
       </c>
       <c r="R3" t="n">
-        <v>7203583</v>
+        <v>7203582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440333</v>
+        <v>113440335</v>
       </c>
       <c r="B4" t="n">
-        <v>90096</v>
+        <v>90099</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772804</v>
+        <v>772748</v>
       </c>
       <c r="R4" t="n">
-        <v>7203582</v>
+        <v>7203574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440336</v>
+        <v>113440334</v>
       </c>
       <c r="B5" t="n">
-        <v>90096</v>
+        <v>90099</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772757</v>
+        <v>772789</v>
       </c>
       <c r="R5" t="n">
-        <v>7203587</v>
+        <v>7203583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440336</v>
+        <v>113440335</v>
       </c>
       <c r="B2" t="n">
-        <v>90099</v>
+        <v>90130</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772757</v>
+        <v>772748</v>
       </c>
       <c r="R2" t="n">
-        <v>7203587</v>
+        <v>7203574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440333</v>
+        <v>113440336</v>
       </c>
       <c r="B3" t="n">
-        <v>90099</v>
+        <v>90130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772804</v>
+        <v>772757</v>
       </c>
       <c r="R3" t="n">
-        <v>7203582</v>
+        <v>7203587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440335</v>
+        <v>113440334</v>
       </c>
       <c r="B4" t="n">
-        <v>90099</v>
+        <v>90130</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772748</v>
+        <v>772789</v>
       </c>
       <c r="R4" t="n">
-        <v>7203574</v>
+        <v>7203583</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440334</v>
+        <v>113440333</v>
       </c>
       <c r="B5" t="n">
-        <v>90099</v>
+        <v>90130</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772789</v>
+        <v>772804</v>
       </c>
       <c r="R5" t="n">
-        <v>7203583</v>
+        <v>7203582</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440335</v>
+        <v>113440333</v>
       </c>
       <c r="B2" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772748</v>
+        <v>772804</v>
       </c>
       <c r="R2" t="n">
-        <v>7203574</v>
+        <v>7203582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>113440336</v>
       </c>
       <c r="B3" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440334</v>
+        <v>113440335</v>
       </c>
       <c r="B4" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772789</v>
+        <v>772748</v>
       </c>
       <c r="R4" t="n">
-        <v>7203583</v>
+        <v>7203574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113440333</v>
+        <v>113440334</v>
       </c>
       <c r="B5" t="n">
-        <v>90130</v>
+        <v>90131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>772804</v>
+        <v>772789</v>
       </c>
       <c r="R5" t="n">
-        <v>7203582</v>
+        <v>7203583</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113440333</v>
+        <v>113440335</v>
       </c>
       <c r="B2" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>772804</v>
+        <v>772748</v>
       </c>
       <c r="R2" t="n">
-        <v>7203582</v>
+        <v>7203574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113440336</v>
+        <v>113440333</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>772757</v>
+        <v>772804</v>
       </c>
       <c r="R3" t="n">
-        <v>7203587</v>
+        <v>7203582</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113440335</v>
+        <v>113440336</v>
       </c>
       <c r="B4" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>772748</v>
+        <v>772757</v>
       </c>
       <c r="R4" t="n">
-        <v>7203574</v>
+        <v>7203587</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>113440334</v>
       </c>
       <c r="B5" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 9652-2023 artfynd.xlsx
+++ b/artfynd/A 9652-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
